--- a/data/trans_orig/IP07_C15_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C15_2023-Habitat-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han producido situaciones de cyberbulling fuera de su colegio en 2023 (tasa de respuesta: 92,89%)</t>
+          <t>Menores según si se han producido situaciones de cyberbulling fuera de su colegio/instituto en 2023 (tasa de respuesta: 92,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3816</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7733</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,26%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,73%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1531</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>415</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3991</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>443</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10690</t>
+          <t>10802</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42398</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>38481</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>44847</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,74%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>83,27%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,04%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>29087</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>26627</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30203</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>95,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>86,96%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42652</t>
+          <t>31984</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38005</t>
+          <t>29579</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45335</t>
+          <t>33141</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>71739</t>
+          <t>74383</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66584</t>
+          <t>68996</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74692</t>
+          <t>77301</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>46214</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>46214</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>46214</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>30618</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>30618</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>30618</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46656</t>
+          <t>33584</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46656</t>
+          <t>33584</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46656</t>
+          <t>33584</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>77274</t>
+          <t>79798</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>77274</t>
+          <t>79798</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>77274</t>
+          <t>79798</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10923</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5708</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19584</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,78%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,32%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5020</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2243</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9059</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>9,75%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12189</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20593</t>
+          <t>9842</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>16091</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11048</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26396</t>
+          <t>24839</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>90427</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>81766</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>95642</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,22%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>80,68%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,37%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>46486</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>42447</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>49263</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>90,25%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>82,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,64%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>89992</t>
+          <t>49936</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81588</t>
+          <t>45262</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95714</t>
+          <t>52802</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>136478</t>
+          <t>140363</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>127291</t>
+          <t>131615</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>142639</t>
+          <t>146153</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>101350</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>101350</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>101350</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>51506</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>51506</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>51506</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>102181</t>
+          <t>55104</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>102181</t>
+          <t>55104</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>102181</t>
+          <t>55104</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>153687</t>
+          <t>156454</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>153687</t>
+          <t>156454</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>153687</t>
+          <t>156454</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2846</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>884</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7198</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,57%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6449</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1685</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12759</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,23%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17460</t>
+          <t>15502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>48224</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>43872</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>50186</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,43%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>63389</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>57079</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>68153</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>90,77%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>81,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,59%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48617</t>
+          <t>40341</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43484</t>
+          <t>34961</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50687</t>
+          <t>43566</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>112005</t>
+          <t>88565</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103859</t>
+          <t>82504</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>117179</t>
+          <t>92705</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>51070</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>51070</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>51070</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>69838</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>69838</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>69838</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>51481</t>
+          <t>46936</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51481</t>
+          <t>46936</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51481</t>
+          <t>46936</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>121319</t>
+          <t>98006</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>121319</t>
+          <t>98006</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>121319</t>
+          <t>98006</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8881</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4822</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15562</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17,85%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,69%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,28%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8260</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4677</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13805</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>17,64%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9315</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15437</t>
+          <t>14109</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>17576</t>
+          <t>17463</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>11449</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24795</t>
+          <t>25208</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>40867</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34186</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>44926</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>82,15%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>68,72%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,31%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>38573</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>33028</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>42156</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>82,36%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>70,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,01%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40750</t>
+          <t>41197</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34628</t>
+          <t>35669</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45590</t>
+          <t>45524</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>79322</t>
+          <t>82063</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>72103</t>
+          <t>74318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>85489</t>
+          <t>88077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,5%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>49748</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>49748</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>49748</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>46833</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>46833</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>46833</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50065</t>
+          <t>49778</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50065</t>
+          <t>49778</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50065</t>
+          <t>49778</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>96898</t>
+          <t>99526</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>96898</t>
+          <t>99526</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>96898</t>
+          <t>99526</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>26465</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18627</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>37449</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,5%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>21260</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>11854</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>30319</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10,69%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>15,25%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>28374</t>
+          <t>21944</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19212</t>
+          <t>15458</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40210</t>
+          <t>30076</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>49633</t>
+          <t>48409</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36702</t>
+          <t>37331</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63756</t>
+          <t>60644</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>221917</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>210933</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>229755</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>89,35%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>84,92%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,5%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>177535</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>168476</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>186941</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>89,31%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>84,75%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,04%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>222009</t>
+          <t>163457</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>210173</t>
+          <t>155325</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>231171</t>
+          <t>169943</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>399545</t>
+          <t>385374</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>385422</t>
+          <t>373139</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>412476</t>
+          <t>396452</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>248382</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>248382</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>248382</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>198795</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>198795</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>198795</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>250383</t>
+          <t>185401</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>250383</t>
+          <t>185401</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>250383</t>
+          <t>185401</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>449178</t>
+          <t>433783</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>449178</t>
+          <t>433783</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>449178</t>
+          <t>433783</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
